--- a/data/trans_orig/IP16B98-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16B98-Clase-trans_orig.xlsx
@@ -801,7 +801,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2569</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>63,53%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3426</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4577</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10388</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15708</t>
+          <t>15717</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>2593</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5140</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>633</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5962</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>37,34%</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12387</t>
+          <t>12448</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16125</t>
+          <t>16619</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31245</t>
+          <t>31243</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37465</t>
+          <t>37044</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5821</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>6892</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2226</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>53,97%</t>
         </is>
       </c>
     </row>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3256</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11181</t>
+          <t>11255</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,08%</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18508</t>
+          <t>18082</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16536</t>
+          <t>16423</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36518</t>
+          <t>36820</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41655</t>
+          <t>41644</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2596</t>
+          <t>3022</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>4672</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>555</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t>5379</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
